--- a/forecast/conditions/conditions_worklist.xlsx
+++ b/forecast/conditions/conditions_worklist.xlsx
@@ -13,14 +13,14 @@
     <sheet name="B · redistricting plans" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="C · redistricting events" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="D · confirm my drops" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="E · only you can get this" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="E · decisions and open items" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'A · dates to verify'!$A$2:$K$13</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'B · redistricting plans'!$A$2:$L$17</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'C · redistricting events'!$A$2:$N$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'A · dates to verify'!$A$2:$L$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'B · redistricting plans'!$A$2:$L$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'C · redistricting events'!$A$2:$O$73</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'D · confirm my drops'!$A$2:$H$40</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'E · only you can get this'!$A$2:$H$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'E · decisions and open items'!$A$2:$F$12</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="573">
   <si>
     <t xml:space="preserve">Conditions worklist</t>
   </si>
@@ -58,19 +58,19 @@
     <t xml:space="preserve">A · dates to verify</t>
   </si>
   <si>
-    <t xml:space="preserve">10 rows the machine could not settle: four seats with two names for one member, three dates that are upper bounds, three one-day entries. The smallest sheet and the most valuable.</t>
+    <t xml:space="preserve">YOUR ANSWERS, carried over, with my review in the last column. Six are clean. Four need one more touch.</t>
   </si>
   <si>
     <t xml:space="preserve">B · redistricting plans</t>
   </si>
   <si>
-    <t xml:space="preserve">14 states. Names the plans so sheet C has something to point at.</t>
+    <t xml:space="preserve">PRE-FILLED. 20 rows now — every state that redrew or tried — with a column that settles which of them actually changed a district, from your own Cook capture.</t>
   </si>
   <si>
     <t xml:space="preserve">C · redistricting events</t>
   </si>
   <si>
-    <t xml:space="preserve">28 dated status rows, of which 11 are real transitions.</t>
+    <t xml:space="preserve">PRE-FILLED. 70 dated rows in one timeline: 28 from our archive's status table and 41 from outside it, covering both waves end to end.</t>
   </si>
   <si>
     <t xml:space="preserve">D · confirm my drops</t>
@@ -79,28 +79,37 @@
     <t xml:space="preserve">37 rows I think are duplicates or consequences. Scanning, not typing.</t>
   </si>
   <si>
+    <t xml:space="preserve">E · decisions and open items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A log now, not a list of asks. Seven of nine closed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where the data came from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecast/collect/wiki_firstseen.py reads the stored revisions and writes conditions/drafts/. conditions_audit.py flags the rows. Both re-run any time; this workbook is a snapshot of one run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When is a map 'in effect'?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The workbook uses one test: a map is in effect when it governs the ballot that actually gets printed. That is the only definition a seat forecast can use, because a seat forecast is a claim about ballots. Virginia is the hard case — the referendum passed, so in a real sense 'that was the map' for seventeen days — but no map was ever drawn under it and no ballot was ever going to carry it, so in_effect_for_2026 stays 'no' throughout. What changed in those seventeen days was expectation, not districts, and expectation is what the markets price rather than what this table records.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it cannot tell you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wikipedia dates the EDIT, not the event. Median lag in this run looks like a day, but the rows in sheet A are the ones where it is worse, or where the fact was already on the page before we started watching and the true date is earlier than anything we hold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress</t>
+  </si>
+  <si>
     <t xml:space="preserve">E · only you can get this</t>
   </si>
   <si>
-    <t xml:space="preserve">8 asks that are not in any archive. The district baselines are the blocker; the rest are minutes each.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where the data came from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forecast/collect/wiki_firstseen.py reads the stored revisions and writes conditions/drafts/. conditions_audit.py flags the rows. Both re-run any time; this workbook is a snapshot of one run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What it cannot tell you</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wikipedia dates the EDIT, not the event. Median lag in this run looks like a day, but the rows in sheet A are the ones where it is worse, or where the fact was already on the page before we started watching and the true date is earlier than anything we hold.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The rows where the machine cannot settle it. Ten of 128. Fill the yellow columns; grey is context. `event_date` is when it HAPPENED — leave it blank rather than copying our date, which is only when the page said so.</t>
+    <t xml:space="preserve">YOUR ANSWERS, carried over verbatim, with my review in the last column. Six rows are clean and ready to merge. Four need one more touch — read `my review`.</t>
   </si>
   <si>
     <t xml:space="preserve">person</t>
@@ -136,6 +145,9 @@
     <t xml:space="preserve">notes</t>
   </si>
   <si>
+    <t xml:space="preserve">my review</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXAMPLE — delete this row</t>
   </si>
   <si>
@@ -184,6 +196,18 @@
     <t xml:space="preserve"># AZ-7: Raúl Grijalva is retiring.</t>
   </si>
   <si>
+    <t xml:space="preserve">2024-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kjzz.org/elections/2024-10-01/u-s-rep-raul-grijalva-wont-run-again-in-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Announced in KOLD-TV interview on Oct 1, 2024; later died in office March 13, 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOD, and it needs a second row. He announced 2024-10-01 — BEFORE the term starts — so known_by becomes 2024-10-01 too and this row sits outside the site's 2025-01-20 frame, which is correct for a conditions table. But he then died in office on 2025-03-13, and that is a separate dated event this table should hold: add a `died` row. The 2026 incumbent for AZ-7 is the special-election winner, not him, so incumbent_on_ballot_after needs care here.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cory Mills</t>
   </si>
   <si>
@@ -196,6 +220,21 @@
     <t xml:space="preserve"># FL-7: Cory Mills is retiring to run for U.S. Senate.</t>
   </si>
   <si>
+    <t xml:space="preserve">lost primary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[https://ballotpedia.org/Florida%27s_7th_Congressional_District_election,_2026_(August_18_Republican_primary](https://ballotpedia.org/Florida%27s_7th_Congressional_District_election,_2026_(August_18_Republican_primary))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did not run for Senate; ran for re-election in FL-07 and lost the Republican primary on August 18, 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TYPO: 'lost primary' should be `lost_primary` — the vocabulary is underscored and a space makes it a new category. Bigger question: this row's known_by belongs to the SENATE claim the page made in January 2025, which you have now established never happened. Two honest options — (a) keep only the lost_primary event dated 2026-08-18 and note the abandoned Senate bid, or (b) keep both, with an `unretired` row in between when he filed for re-election. I lean (a) unless you want the abandoned bid in the timeline. Also the source_url is a doubled markdown link and needs unwrapping.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Danny K. Davis</t>
   </si>
   <si>
@@ -211,6 +250,18 @@
     <t xml:space="preserve"># IL-7: Danny K. Davis is retiring.</t>
   </si>
   <si>
+    <t xml:space="preserve">2025-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[https://www.cbsnews.com/chicago/news/congressman-danny-davis-retiring-endorses-la-shawn-ford/](https://www.cbsnews.com/chicago/news/congressman-danny-davis-retiring-endorses-la-shawn-ford/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary record. Formally announced retirement on July 31, 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOD, and worth noticing that event_date (07-31) is AFTER known_by (07-30). That is not an error here — the page carried the news a day before the formal announcement — but it is exactly the pattern that flags a genuine date mix-up elsewhere, so I would leave your note in place explaining it. source_url is a doubled markdown link; needs unwrapping.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Danny Davis</t>
   </si>
   <si>
@@ -220,6 +271,15 @@
     <t xml:space="preserve"># IL-7: Danny Davis is retiring.</t>
   </si>
   <si>
+    <t xml:space="preserve">drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate entry due to missing middle initial in table cell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREED. Clean drop.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Al Green</t>
   </si>
   <si>
@@ -235,6 +295,15 @@
     <t xml:space="preserve"># TX-9: Al Green is retiring due to redistricting.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://ballotpedia.org/Texas%27_18th_Congressional_District_election,_2026_(March_3_Democratic_primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stale entry. Did not retire; ran in TX-18 following Texas redistricting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREED that it is not a retirement, but this is NOT nothing. He moved from TX-09 to TX-18 because of the Texas redraw, and our schema has no event type for an incumbent switching districts. That matters for any incumbency term: TX-09 loses its incumbent without a retirement, and TX-18 gains one who is not its 2024 incumbent. Suggest adding `switched_district` to the vocabulary and recording it with the TX-2025-hb4 plan_id.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tim Walz</t>
   </si>
   <si>
@@ -250,6 +319,15 @@
     <t xml:space="preserve">! Minnesota | Tim | Walz (retiring) | data-sort-value="-52.3" | 52.27% DFL</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.theguardian.com/us-news/2026/jan/05/tim-walz-minnesota-governor-reelection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes: Withdrew from running for a third term as Minnesota Governor on January 5, 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREED. Clean keep. (Your notes cell has 'notes:' doubled at the front.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peggy Bennett</t>
   </si>
   <si>
@@ -259,6 +337,15 @@
     <t xml:space="preserve">! Minnesota | Tim | Walz | DFL | 2018 | data-sort-value=-52.3 | 52.3% DFL | Incumbent retiring | nowrap | {{Plainlist | * Peggy Bennett (Republican)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/2026_Minnesota_gubernatorial_election</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes: Misread table cell twin; drop to keep the Tim Walz primary governor record clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREED. Clean drop — she is a challenger listed in the incumbent row's candidate cell. (Your notes cell also has 'notes:' doubled.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sharice Davids</t>
   </si>
   <si>
@@ -271,6 +358,15 @@
     <t xml:space="preserve">! KS-3 | Sharice | Davids (retiring) | data-sort-value=-53.4 | 53.4% D</t>
   </si>
   <si>
+    <t xml:space="preserve">https://ballotpedia.org/Kansas%27_3rd_Congressional_District_election,_2026_(August_4_Democratic_primary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stale single-day entry. Did not retire; ran for re-election in KS-03.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREED, and this one is worth keeping a record of: a fact that was on the page for a single day and was never true. It is the clearest evidence in the set that the `low` / one-day grade is doing real work.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tony Gonzales</t>
   </si>
   <si>
@@ -289,25 +385,40 @@
     <t xml:space="preserve">withdrew</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-03-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.texastribune.org/2026/03/05/tony-gonzales-drops-out-republican-primary-texas-23rd-district-congress/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropped out of the primary runoff and announced he would not seek re-election on March 5, 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOD. Note event_date 2026-03-05 is one day BEFORE known_by 2026-03-06, which is the normal direction and a small confirmation that the extractor's dates are landing about a day late, as expected.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-03-14</t>
   </si>
   <si>
     <t xml:space="preserve"># TX-23: Tony Gonzales was originally set to run in a runoff, but he withdrew.</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per state whose redistricting status moved at all. `plan_id` is the join key for sheet C — use STATE-YYYY-shortname, e.g. TX-2026-hb1. `baseline_file` names the per-district PVI file in the PRIVATE repo; no baseline numbers go in this workbook.</t>
+    <t xml:space="preserve">Duplicate entry merged into Row 10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREED. Your note says 'merged into Row 10' — it is row 12 in this sheet. Cosmetic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRE-FILLED. One row per state that redrew or tried to. The third column is the one that settles 'did it actually happen': it counts districts whose Cook PVI moved between pvi_prior and pvi in the capture already in your private repo. Yellow = please check. Read the Virginia row.</t>
   </si>
   <si>
     <t xml:space="preserve">state</t>
   </si>
   <si>
-    <t xml:space="preserve">first status we saw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">latest status we saw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status changes</t>
+    <t xml:space="preserve">wiki status, first -&gt; last</t>
+  </si>
+  <si>
+    <t xml:space="preserve">districts whose PVI moved</t>
   </si>
   <si>
     <t xml:space="preserve">plan_id</t>
@@ -331,124 +442,391 @@
     <t xml:space="preserve">baseline_file</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-07-31 · Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-29 · Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX-2026-hb1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House Bill 1 (2025 special session)</t>
+    <t xml:space="preserve">checked?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Pending legislative action -&gt; 2025-08-29 Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 of 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XX-2025-hb1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Bill 1</t>
   </si>
   <si>
     <t xml:space="preserve">legislature</t>
   </si>
   <si>
-    <t xml:space="preserve">Cook Political Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pvi_TX_2026_hb1.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signed 2025-08-22, enjoined 2025-08-29</t>
+    <t xml:space="preserve">+3 R (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ballotpedia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cook_pvi/...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signed 2025-08-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Pending legislative action  -&gt;  2025-08-29 Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 of 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX-2025-hb4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Bill 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5 R (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ballotpedia.org/Redistricting_ahead_of_the_2026_elections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cook_pvi/2026-08-19/manual.json (pvi_prior = old map, pvi = new)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-decade partisan redraw. Quorum break 2025-08-03; signed 2025-08-29. 29 of 38 districts moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-09 Pending legislative action  -&gt;  2025-11-05 New districts enacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 of 52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA-2025-prop50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legislature map, ratified at the 2025-11-04 special election</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legislature + voters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5 D (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needed a constitutional amendment at the ballot, so the enactment date is the election, not the signing. The California counterpart to Virginia: same mechanism, opposite outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-04 New districts enacted  -&gt;  2025-11-04 New districts enacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 of 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MO-2025-special</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special-session congressional map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 R (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/2025%E2%80%932026_United_States_redistricting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED: signed 2025-09-28, not merely proposed on 08-29. Missouri Supreme Court upheld it 4-3 on 2026-03-24. A citizens' initiative to refer it is still live, so this is the one enacted map whose status could still move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-29 Pending legislative action  -&gt;  2025-10-31 New districts enacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OH-2025-required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four-year replacement map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legislature / redistricting commission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">our archive · House elections page status table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT a partisan mid-decade redraw: the 2018 amendment required a new map by 2025-11-20 because the 2022 map passed without bipartisan support.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Litigation pending  -&gt;  2025-08-26 Pending legislative action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 of 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UT-2025-court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaintiff Map 1, imposed by the court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTED and more tangled than the first pass had it: the 2021 map fell 2025-08-25; the legislature passed a replacement 2025-10-06; Judge Gibson held THAT one also violated Proposition 4 on 2025-11-10 and imposed the plaintiffs' map, creating a safe Democratic seat. A repeal petition failed 2026-03-26.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not in the status table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 of 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NC-2025-map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 congressional map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed 2025-10-22 and became law without the governor's signature, which North Carolina does not require for redistricting. Targeted NC-01. Two districts moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Previous districts left in place  -&gt;  2025-11-16 Districts left in place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 of 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL-2026-postcallais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 congressional map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+4 R (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The largest wave-2 redraw: 16 of 28 districts moved. Proclamation 2026-01-07, special session 2026-04-20..24, passed 2026-04-29, signed 2026-05-04.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Previous districts left in place  -&gt;  2025-10-14 Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 of 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA-2026-postcallais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Callais replacement map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callais struck the second majority-Black district. Primaries delayed; new map passed 2026-05-29 altering LA-06. Facing further challenge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 of 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN-2026-postcallais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extraordinary session called by Governor Lee targeting TN-09. Passed and signed the same day, 2026-05-07. Judge Campbell declined to block it 2026-05-26.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 of 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL-2026-postcallais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 special-session map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed CONDITIONALLY, to take effect only if the Allen v. Milligan injunction were lifted — which the Supreme Court did 2026-06-02, 6-3, by unsigned emergency order. Removes the majority-Black district the courts had added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-23 Pending legislative action  -&gt;  2025-10-23 Pending legislative action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 — the map did not change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA-2026-amendment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use of Legislative Congressional Redistricting Map Amendment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2-3 D (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/2026_Virginia_redistricting_referendum · https://www.npr.org/2026/05/08/nx-s1-5805193/redistricting-virginia-trump-midterms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESOLVED. Approved at referendum 2026-04-21 (51.69/48.31); the state supreme court threw out the referendum RESULT on 2026-05-08, 4-3, for procedural defects in placing it on the ballot; SCOTUS declined the emergency appeal 2026-05-15. A map WAS drawn — HB 29, signed contingently 2026-02-20 — but it never governed a ballot, and the commission map stands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FL-2025-attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Committee on Congressional Redistricting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 2025 Florida attempt, which produced no map. Kept apart from FL-2026-postcallais so 2025 status rows are not bolted onto a plan that did not exist yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-27 Pending legislative action  -&gt;  2025-10-27 Pending legislative action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN-2025-attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special-session map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2 R (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAILED, and the most consequential failure in the set. Session called 2025-10-27; House passed a map targeting IN-01 and IN-07 on 2025-12-05; the Senate rejected it 2025-12-11 with 21 Republicans against. At least five of those Republicans lost renomination in 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD-2025-commission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governor's Redistricting Advisory Commission map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 D (intended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAILED. Commission recommended 2025-12-18 and again 2026-01-20 for MD-01; the House passed it 99-37 on 2026-02-02; the Senate President declined to bring it to a vote, which killed it without a recorded defeat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KS-2025-attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAILED. Budget for a special session approved, votes never there; the regular-session effort stalled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-30 Litigation pending  -&gt;  2025-10-24 Districts left in place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-2026-attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAILED. The House extended the calendar for redistricting; the Senate adjourned 2026-05-26 without ending debate, by which point primary voting had already begun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-30 Pending judicial action  -&gt;  2025-11-01 Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NY-2026-court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOCKED. A state judge struck the lines of the city's only Republican-held seat in January 2026; the U.S. Supreme Court blocked the redraw 2026-03-02 and the original lines stand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Previous districts left in place  -&gt;  2025-10-01 Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WI-litigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">litigants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO CHANGE. Felton v. Wisconsin Elections Commission declined; Bothfeld v. WEC and WBLD v. WEC both rejected. The 6-2 map stands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-31 Litigation pending  -&gt;  2025-07-31 Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA-litigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO CHANGE. In litigation through the window; the master chronology documents no Georgia action and no district moved.</t>
   </si>
   <si>
     <t xml:space="preserve">AR</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-07-31 · Previous districts left in place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-24 · Districts left in place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-09 · Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-05 · New districts enacted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-16 · Districts left in place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-31 · Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-27 · Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-14 · Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-04 · New districts enacted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-30 · Pending judicial action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-01 · Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-29 · Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-31 · New districts enacted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-30 · Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-26 · Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-23 · Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-01 · Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every dated move in the Wikipedia status table. `kind = CHANGE` is a real transition; `status we inherited` is what a state already showed when we started watching, so it is NOT an event; `wording change?` is probably nothing. Map `status after (page's words)` onto our vocabulary: proposed · enacted · enjoined · dead · in_effect.</t>
+    <t xml:space="preserve">2025-07-31 Previous districts left in place  -&gt;  2025-10-24 Districts left in place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR-2025-status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO CHANGE. Appears in our status table only; previous districts left in place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRE-FILLED. Sorted by date so it reads as one timeline. Rows marked 'our archive' come from the status table the House elections page carried from 2025-07-31 until it was DELETED on 2026-01-24 — which is exactly why every post-Callais event had to come from elsewhere and is marked '(outside the table)'. I guessed `status_after` and `in_effect_for_2026` from the page's wording; check them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">known_by</t>
   </si>
   <si>
     <t xml:space="preserve">kind</t>
@@ -460,7 +838,7 @@
     <t xml:space="preserve">status after (page's words)</t>
   </si>
   <si>
-    <t xml:space="preserve">date error bar (days)</t>
+    <t xml:space="preserve">where it came from</t>
   </si>
   <si>
     <t xml:space="preserve">event_type</t>
@@ -481,43 +859,160 @@
     <t xml:space="preserve">CHANGE</t>
   </si>
   <si>
+    <t xml:space="preserve">Pending legislative action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litigation pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">our archive · wiki status table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">court_ruling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enjoined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LULAC v. Texas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://example.org/order.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">three-judge panel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHANGE (outside the table)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">introduced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proposed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-day special session began</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status we inherited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous districts left in place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not an event — this is the state's status on the first day we hold it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending legislative action and referendum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passed_chamber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House approved HB 4, 88-52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending referendum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passed_legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legislature passed the bills; Governor signed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pending legislative action and litigation pending</t>
   </si>
   <si>
-    <t xml:space="preserve">Litigation pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">court_ruling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enjoined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LULAC v. Texas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://example.org/order.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">three-judge panel, stayed pending appeal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status we inherited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Previous districts left in place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
+    <t xml:space="preserve">'litigation pending' has no equivalent in our five statuses: it says a case exists, not that the map is blocked. Fill status_after with what was actually in effect that day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senate approved, 18-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">League of Women Voters v. Utah State Legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 2021 map struck down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governor Kehoe announced the special session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governor Abbott signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORRECTION to the earlier draft, which had this map as merely proposed: Kehoe signed it on this date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The legislature's replacement map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Became law without the governor's signature, which NC does not require for redistricting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-23</t>
   </si>
   <si>
     <t xml:space="preserve">2025-10-24</t>
@@ -529,75 +1024,243 @@
     <t xml:space="preserve">Districts left in place</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending legislative action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending legislative action and referendum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending referendum</t>
+    <t xml:space="preserve">probably nothing — same claim, different words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governor Braun called a special session for Nov 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending judicial action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New districts enacted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First passage (Senate 21-16). Virginia amendments must pass twice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">referendum_approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special election ratified the amendment; our status table flipped to 'New districts enacted' the next day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governor Moore formed the advisory commission</t>
   </si>
   <si>
     <t xml:space="preserve">2025-11-05</t>
   </si>
   <si>
-    <t xml:space="preserve">New districts enacted</t>
+    <t xml:space="preserve">2025-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judge Gibson held the LEGISLATURE'S replacement also violated Proposition 4 and imposed the plaintiffs' Map 1, creating a safe Democratic seat</t>
   </si>
   <si>
     <t xml:space="preserve">2025-11-16</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-10-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending judicial action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-11-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-01</t>
+    <t xml:space="preserve">2025-11-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senate voted to adjourn without acting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three-judge federal panel allowed the map's use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House passed a map targeting IN-01 and IN-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senate rejected it: 21 Republicans and all 10 Democrats against. At least five of those Republicans lost renomination in 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commission_adopted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission voted to recommend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeSantis proclamation calling the 2026-04-20..24 special session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Second passage, sending it to the ballot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission recommended an MD-01 map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House passed 99-37; the Senate President then declined to hold a vote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House Bill 29, signed by Governor Spanberger, DETAILS THE ACTUAL DISTRICT BOUNDARIES — contingently: 'the new districts will not go into effect unless the constitutional amendment is approved by voters.' So a drawn Virginia map does exist on paper, which is what makes a labelled counterfactual run possible at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Supreme Court blocked the state judge's redraw; the original lines stand for 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missouri Supreme Court upheld the map 4-3. A citizens' initiative to refer it is still live.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republican repeal petition failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved 51.69% to 48.31%. in_effect_for_2026 is 'no' because no map was ever drawn under it — see the Read me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.supremecourt.gov/opinions/25pdf/24-109_21o3.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passed the same day as the decision. The signature came 2026-05-04; an earlier draft of this sheet recorded the passage date as the enactment, and it was not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louisiana v. Callais, No. 24-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE PIVOT. 6-3: Louisiana's second majority-Black district was an unconstitutional racial gerrymander, and Section 2 compliance could not justify it. Every wave-2 redraw below hangs off this date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louisiana v. Callais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primaries delayed by the Secretary of State to allow a redraw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governor Ivey called the special session. NOTE: Roll Call reported the CALL on 2026-05-01 and the master chronology dates it 05-04. Three days apart; pick one and say which.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeSantis signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both chambers passed and Governor Lee signed the same day, targeting TN-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virginia Supreme Court, 4-3, threw out the referendum RESULT for procedural defects in placing the amendment on the ballot. Case name still not established.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Supreme Court declined the emergency appeal; the commission map stands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mississippi and North Dakota cases remanded for reconsideration under Callais. No Mississippi district moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senate adjourned until June 10 without ending debate; primary voting had already begun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chief District Judge William L. Campbell Jr. declined the ACLU's request to block the map pending appeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New map altering LA-06 to reduce its Black population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen v. Milligan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Supreme Court, 6-3, unsigned emergency order lifting the Milligan injunction. THIS is the date Alabama's map took effect: the legislature had passed it conditionally, to apply only if the injunction were removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Rows I think should not become events. Two kinds: a generic '(retiring)' from the ratings page that a better row already covers with a reason and an earlier date, and the ratings page marking a seat open, which is a consequence of the announcement rather than the announcement. Scan and write `keep` on anything you disagree with; blank means you agree.</t>
   </si>
   <si>
-    <t xml:space="preserve">known_by</t>
-  </si>
-  <si>
     <t xml:space="preserve">why I want to drop it</t>
   </si>
   <si>
@@ -910,9 +1573,6 @@
     <t xml:space="preserve"># Iowa 2: Open seat</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-08-25</t>
-  </si>
-  <si>
     <t xml:space="preserve"># Kentucky 6: Open seat</t>
   </si>
   <si>
@@ -976,163 +1636,121 @@
     <t xml:space="preserve">#Texas 23: Open seat</t>
   </si>
   <si>
-    <t xml:space="preserve">The eight things that are not recoverable from the archive. The first one is the real blocker; the rest are small.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">what I need</t>
-  </si>
-  <si>
-    <t xml:space="preserve">specifically</t>
-  </si>
-  <si>
-    <t xml:space="preserve">why it matters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">where to look</t>
-  </si>
-  <si>
-    <t xml:space="preserve">format I need</t>
+    <t xml:space="preserve">Now a decisions LOG rather than a list of asks. Seven of nine are closed. The two open ones are the Virginia backfill policy and a handful of court case names.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item</t>
   </si>
   <si>
     <t xml:space="preserve">status</t>
   </si>
   <si>
-    <t xml:space="preserve">link or path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">what exactly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">what breaks without it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a CSV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">private-repo/pvi_TX.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per-plan district baselines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cook PVI, or 2024 presidential two-party, for each district under each ENACTED map version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-running a seat model on the map that was legally in effect at a past date is impossible without the district baselines for that map. This is the one blocker on fixing the backfilled seat projections.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cook Political Report; Dave's Redistricting App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one CSV per plan in the PRIVATE repo, named in sheet B's baseline_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing Senate retirements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Senate page's own summary said eleven senators had announced; we extracted six (Peters, Smith, McConnell, Shaheen, Durbin, Tuberville)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A structural model that takes incumbency needs all of them, and a gap here is invisible rather than noisy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the Senate page's retirements section, or a news roundup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name + state + announcement date + source, straight into sheet A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing governor retirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The gubernatorial page said five governors; we have four (Reynolds, Evers, Bowser, Walz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same reason, smaller stakes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the gubernatorial page's retirements section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same as above</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCOTUS redistricting decision date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The date of the decision you mentioned, and the case name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is the single most important marker on the timeline, and every southern redraw hangs off it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the opinion itself</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one date + case name + link; I will add it to the chart markers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Court case names and order dates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For the states sitting in 'Litigation pending': FL, GA, LA, NY, SC, TX, UT, WI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wikipedia dates when the page changed, not when the court ruled. For litigation the gap can be days, and these are the events markets moved on.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the dockets, or Democracy Docket / Cook's tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case name + order date + link, into sheet C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cook redistricting tracker: what may we use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether their dates and seat-shift estimates may be reproduced, and under what attribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standing rule on this project is no data reproduction on the public side unless the licence permits. Their tracker is the best source and the one most likely to need permission.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">their terms, or an email to them</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a yes/no I can write into sources/2026.yaml notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delegates: in or out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether DC and the territories get rows at all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They are not among the 435 and no other source in the archive has a race for them, so the extractor refuses them a race_id. That is a choice, not a fact.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">your call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">one word</t>
+    <t xml:space="preserve">decision / finding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what changes because of it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agreed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what was decided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what I did about it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double redraws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No state redrew twice since 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Cook capture's single pvi_prior / pvi pair is therefore a COMPLETE baseline for every changed state. The largest item on the original list closes with one sentence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook PVI publication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prior and current PVI may sit in the public data and in models; we just do not display them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs a line in sources/2026.yaml under cook_pvi and a sentence on the methods page saying the values are Cook's, published on their own site, used as model input and not reproduced as a table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">switched_district event type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not needed. An incumbent who moves districts is still an incumbent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convention recorded in conditions/README.md: the member follows his seat, so TX-18 has an incumbent running and TX-09 becomes an open seat. Worth revisiting only if a candidate-quality term ever enters a model, since Al Green faces a large share of voters who have never voted for him.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delegates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already implemented — the extractor refuses a race_id to DC and the territories and marks the row.</t>
   </si>
   <si>
     <t xml:space="preserve">At-large numbering</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether an at-large seat is district 01 or 00 in a race_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I used 01. If anything else in the archive uses 00 they will never join.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">your call, checked against the existing race ids</t>
+    <t xml:space="preserve">00, not 01.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implemented in the extractor. Checked first: NO at-large House race_id exists anywhere in the parsed archive, so nothing had to be migrated and nothing will fail to join.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alabama, Tennessee, Louisiana dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN passed and signed 2026-05-07. LA passed 2026-05-29. AL passed conditionally and took effect 2026-06-02 when SCOTUS lifted the Milligan injunction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One residual: Roll Call dates Ivey's session call to 2026-05-01, the master chronology to 05-04. Three days apart. Pick one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Court case names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSTLY DONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louisiana v. Callais (No. 24-109); Allen v. Milligan (AL); League of Women Voters v. Utah State Legislature (UT); Felton v. WEC, Bothfeld v. WEC and WBLD v. WEC (WI).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STILL OPEN: the Virginia case name, and Georgia, South Carolina and Missouri, for which no case name appears in any source I read.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virginia: backfill or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN — my recommendation inside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run every date on the commission map, because no other map ever governed a ballot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A counterfactual IS possible — HB 29 (signed contingently 2026-02-20) contains the actual boundaries — but it would need a district-level baseline for a map that never took effect, which Cook will not have. Dave's Redistricting App would. Worth it only if you want the scenario beside the markets; not needed for the main line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both Virginia and California needed a ballot step that the vocabulary cannot describe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggest adding `referendum_approved` and `referendum_rejected` to the event_type list in conditions/README.md. Used in sheet C already.</t>
   </si>
 </sst>
 </file>
@@ -1653,7 +2271,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1703,7 +2321,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -1711,7 +2329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1727,7 +2345,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1746,7 +2364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -1754,54 +2372,62 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="B15" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="5" t="str">
-        <f aca="false">COUNTA('A · dates to verify'!G4:G13)&amp;" of 10 rows started"</f>
-        <v>0 of 10 rows started</v>
+      <c r="A17" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B18" s="5" t="str">
-        <f aca="false">COUNTA('B · redistricting plans'!E4:E17)&amp;" of 14 rows started"</f>
-        <v>0 of 14 rows started</v>
+        <f aca="false">COUNTA('A · dates to verify'!L4:L13)&amp;" of 10 rows checked"</f>
+        <v>10 of 10 rows checked</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19" s="5" t="str">
-        <f aca="false">COUNTA('C · redistricting events'!G4:G31)&amp;" of 28 rows started"</f>
-        <v>0 of 28 rows started</v>
+        <f aca="false">COUNTA('B · redistricting plans'!L4:L23)&amp;" of 20 rows checked"</f>
+        <v>0 of 20 rows checked</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B20" s="5" t="str">
-        <f aca="false">COUNTA('D · confirm my drops'!G4:G40)&amp;" of 37 rows started"</f>
-        <v>0 of 37 rows started</v>
+        <f aca="false">COUNTA('C · redistricting events'!O4:O73)&amp;" of 70 rows checked"</f>
+        <v>0 of 70 rows checked</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" s="5" t="str">
-        <f aca="false">COUNTA('E · only you can get this'!F4:F11)&amp;" of 8 rows started"</f>
-        <v>0 of 8 rows started</v>
+        <f aca="false">COUNTA('D · confirm my drops'!G4:G40)&amp;" of 37 rows checked"</f>
+        <v>0 of 37 rows checked</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="5" t="str">
+        <f aca="false">COUNTA('e · only you can get this'!f4:f12)&amp;" of 9 rows checked"</f>
+        <v>1 of 9 rows checked</v>
       </c>
     </row>
   </sheetData>
@@ -1820,7 +2446,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -1834,11 +2460,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1850,331 +2477,442 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="314.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="D4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="H4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="404.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>47</v>
-      </c>
       <c r="E5" s="9" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="10"/>
+        <v>78</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K7" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="10"/>
+        <v>86</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J8" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>94</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="10"/>
+        <v>107</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="K13" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K13"/>
+  <autoFilter ref="A2:L13"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2192,22 +2930,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2223,390 +2965,734 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="H9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>192</v>
+      </c>
       <c r="L9" s="10"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>121</v>
+        <v>193</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+        <v>195</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>199</v>
+      </c>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>124</v>
+        <v>201</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+        <v>202</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>206</v>
+      </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>126</v>
+        <v>207</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+        <v>208</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>210</v>
+      </c>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+        <v>212</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>215</v>
+      </c>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>131</v>
+        <v>216</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>161</v>
+      </c>
       <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>222</v>
+      </c>
       <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="K14" s="10" t="s">
+        <v>223</v>
+      </c>
       <c r="L14" s="10"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
+        <v>195</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>16</v>
+      </c>
       <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>226</v>
+      </c>
       <c r="L15" s="10"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>141</v>
+      </c>
       <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="H16" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>170</v>
+      </c>
       <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="K16" s="10" t="s">
+        <v>232</v>
+      </c>
       <c r="L16" s="10"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>236</v>
+      </c>
       <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>170</v>
+      </c>
       <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="K17" s="10" t="s">
+        <v>238</v>
+      </c>
       <c r="L17" s="10"/>
     </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="L23" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L17"/>
+  <autoFilter ref="A2:L23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -2626,24 +3712,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2658,139 +3746,157 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>141</v>
+        <v>267</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>142</v>
+        <v>268</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>143</v>
+        <v>269</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>146</v>
+        <v>272</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="B4" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="H4" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="N4" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>107</v>
+        <v>259</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>160</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -2799,24 +3905,27 @@
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
+      <c r="N5" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -2825,26 +3934,27 @@
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N6" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>166</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>168</v>
+        <v>276</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -2853,26 +3963,27 @@
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N7" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>168</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
-        <v>170</v>
+        <v>291</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -2881,26 +3992,27 @@
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
+      <c r="N8" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>170</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -2909,24 +4021,27 @@
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
+      <c r="N9" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -2935,26 +4050,27 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
+      <c r="N10" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>160</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D11" s="9"/>
       <c r="E11" s="9" t="s">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -2963,24 +4079,27 @@
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="N11" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>158</v>
+        <v>293</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9" t="s">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -2989,26 +4108,33 @@
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N12" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>174</v>
+        <v>294</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -3016,53 +4142,69 @@
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>158</v>
+        <v>296</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
@@ -3070,133 +4212,182 @@
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>176</v>
+        <v>299</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="H16" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>299</v>
+      </c>
       <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M16" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="O16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>177</v>
+        <v>299</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" s="9"/>
+        <v>274</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>275</v>
+      </c>
       <c r="E17" s="9" t="s">
-        <v>178</v>
+        <v>303</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G17" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>150</v>
+      </c>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N17" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="B19" s="9" t="s">
-        <v>147</v>
+        <v>307</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
       <c r="D19" s="9"/>
-      <c r="E19" s="9" t="s">
-        <v>166</v>
-      </c>
+      <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+        <v>170</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="O19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G20" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -3204,51 +4395,63 @@
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="9" t="s">
-        <v>150</v>
-      </c>
+      <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
+        <v>170</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>273</v>
+      </c>
       <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="M21" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="O21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>150</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -3257,80 +4460,99 @@
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N22" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>162</v>
+        <v>273</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>160</v>
+        <v>303</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="10"/>
+        <v>277</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>150</v>
+      </c>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N23" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
       <c r="D24" s="9"/>
-      <c r="E24" s="9" t="s">
-        <v>166</v>
-      </c>
+      <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
+        <v>153</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>273</v>
+      </c>
       <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M24" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>169</v>
+        <v>315</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>166</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="9" t="s">
-        <v>149</v>
+        <v>276</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -3339,80 +4561,101 @@
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N25" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>147</v>
+        <v>316</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>149</v>
+        <v>276</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>150</v>
+        <v>291</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
+      <c r="I26" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>280</v>
+      </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>158</v>
+        <v>318</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
       <c r="D27" s="9"/>
-      <c r="E27" s="9" t="s">
-        <v>150</v>
-      </c>
+      <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
+        <v>170</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>318</v>
+      </c>
       <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M27" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>132</v>
+        <v>250</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>183</v>
+        <v>320</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>150</v>
+        <v>291</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
@@ -3421,50 +4664,68 @@
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N28" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>159</v>
+        <v>286</v>
       </c>
       <c r="D29" s="9"/>
-      <c r="E29" s="9" t="s">
-        <v>166</v>
-      </c>
+      <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
+        <v>170</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>321</v>
+      </c>
       <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M29" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>158</v>
+        <v>323</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D30" s="9"/>
+        <v>274</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="E30" s="9" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -3473,40 +4734,1608 @@
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N30" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>185</v>
+        <v>324</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>150</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
+        <v>170</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>324</v>
+      </c>
       <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
+      <c r="M31" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="O31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="O33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="O34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="O36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="O39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O40" s="10"/>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="O41" s="10"/>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="O42" s="10"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O43" s="10"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+    </row>
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="O45" s="10"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="O46" s="10"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="O47" s="10"/>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="O48" s="10"/>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="O49" s="10"/>
+    </row>
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="O50" s="10"/>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="O51" s="10"/>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="O52" s="10"/>
+    </row>
+    <row r="53" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="O53" s="10"/>
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="O54" s="10"/>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="O55" s="10"/>
+    </row>
+    <row r="56" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N56" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="O56" s="10"/>
+    </row>
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="O57" s="10"/>
+    </row>
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="O58" s="10"/>
+    </row>
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="O59" s="10"/>
+    </row>
+    <row r="60" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N60" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="O60" s="10"/>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="O61" s="10"/>
+    </row>
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="N62" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="O62" s="10"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="O63" s="10"/>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="J64" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="O64" s="10"/>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J65" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="O65" s="10"/>
+    </row>
+    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J66" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N66" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="O66" s="10"/>
+    </row>
+    <row r="67" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J67" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="O67" s="10"/>
+    </row>
+    <row r="68" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="O68" s="10"/>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="O69" s="10"/>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N70" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="O70" s="10"/>
+    </row>
+    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="O71" s="10"/>
+    </row>
+    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="O72" s="10"/>
+    </row>
+    <row r="73" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="O73" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N31"/>
+  <autoFilter ref="A2:O73"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3538,7 +6367,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>186</v>
+        <v>408</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3550,492 +6379,492 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>143</v>
+        <v>269</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>188</v>
+        <v>409</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>189</v>
+        <v>410</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>191</v>
+        <v>412</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>192</v>
+        <v>413</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>193</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>194</v>
+        <v>415</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>195</v>
+        <v>416</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>185</v>
+        <v>320</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>196</v>
+        <v>417</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>197</v>
+        <v>418</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>198</v>
+        <v>419</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>199</v>
+        <v>420</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>200</v>
+        <v>421</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>201</v>
+        <v>422</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>202</v>
+        <v>423</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>203</v>
+        <v>424</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>204</v>
+        <v>425</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>205</v>
+        <v>426</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>206</v>
+        <v>427</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>207</v>
+        <v>428</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>208</v>
+        <v>429</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>209</v>
+        <v>430</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>210</v>
+        <v>431</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>211</v>
+        <v>432</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>212</v>
+        <v>433</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>213</v>
+        <v>434</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>214</v>
+        <v>435</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>215</v>
+        <v>436</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>216</v>
+        <v>437</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>217</v>
+        <v>438</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>219</v>
+        <v>440</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>220</v>
+        <v>441</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>221</v>
+        <v>442</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>222</v>
+        <v>443</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>223</v>
+        <v>444</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>224</v>
+        <v>445</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>225</v>
+        <v>446</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>226</v>
+        <v>447</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>227</v>
+        <v>448</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>228</v>
+        <v>449</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>229</v>
+        <v>450</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>230</v>
+        <v>451</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>231</v>
+        <v>452</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>232</v>
+        <v>453</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>233</v>
+        <v>454</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>234</v>
+        <v>455</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>235</v>
+        <v>456</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>237</v>
+        <v>458</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>238</v>
+        <v>459</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>239</v>
+        <v>460</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>240</v>
+        <v>461</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>241</v>
+        <v>462</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>242</v>
+        <v>463</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>243</v>
+        <v>464</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>244</v>
+        <v>465</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>245</v>
+        <v>466</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>246</v>
+        <v>467</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>247</v>
+        <v>468</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>248</v>
+        <v>469</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>249</v>
+        <v>470</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>250</v>
+        <v>471</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>251</v>
+        <v>472</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>252</v>
+        <v>473</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>253</v>
+        <v>474</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>254</v>
+        <v>475</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>255</v>
+        <v>476</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>256</v>
+        <v>477</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>190</v>
+        <v>411</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>257</v>
+        <v>478</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>258</v>
+        <v>479</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>259</v>
+        <v>480</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>260</v>
+        <v>481</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>261</v>
+        <v>482</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>262</v>
+        <v>483</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>263</v>
+        <v>484</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>264</v>
+        <v>485</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>265</v>
+        <v>486</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>261</v>
+        <v>482</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>266</v>
+        <v>487</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>267</v>
+        <v>488</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>268</v>
+        <v>489</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>269</v>
+        <v>490</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>261</v>
+        <v>482</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>270</v>
+        <v>491</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>271</v>
+        <v>492</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>272</v>
+        <v>493</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>273</v>
+        <v>494</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>261</v>
+        <v>482</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>274</v>
+        <v>495</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>275</v>
+        <v>496</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>276</v>
+        <v>497</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>277</v>
+        <v>498</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>278</v>
+        <v>499</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>279</v>
+        <v>500</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>280</v>
+        <v>501</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -4043,19 +6872,19 @@
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="B24" s="9" t="s">
-        <v>195</v>
+        <v>416</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>281</v>
+        <v>502</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>283</v>
+        <v>504</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -4063,19 +6892,19 @@
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>284</v>
+        <v>505</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>285</v>
+        <v>506</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>286</v>
+        <v>507</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -4083,19 +6912,19 @@
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9"/>
       <c r="B26" s="9" t="s">
-        <v>287</v>
+        <v>508</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>288</v>
+        <v>509</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>289</v>
+        <v>510</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -4103,19 +6932,19 @@
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9"/>
       <c r="B27" s="9" t="s">
-        <v>211</v>
+        <v>432</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>290</v>
+        <v>511</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>291</v>
+        <v>512</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -4123,19 +6952,19 @@
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9"/>
       <c r="B28" s="9" t="s">
-        <v>260</v>
+        <v>481</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>293</v>
+        <v>513</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
@@ -4143,19 +6972,19 @@
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9"/>
       <c r="B29" s="9" t="s">
-        <v>219</v>
+        <v>440</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>288</v>
+        <v>509</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>294</v>
+        <v>514</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
@@ -4163,19 +6992,19 @@
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9"/>
       <c r="B30" s="9" t="s">
-        <v>295</v>
+        <v>515</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>296</v>
+        <v>516</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>297</v>
+        <v>517</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -4183,19 +7012,19 @@
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9"/>
       <c r="B31" s="9" t="s">
-        <v>265</v>
+        <v>486</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>298</v>
+        <v>518</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -4203,19 +7032,19 @@
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9"/>
       <c r="B32" s="9" t="s">
-        <v>299</v>
+        <v>519</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>285</v>
+        <v>506</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>300</v>
+        <v>520</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
@@ -4223,19 +7052,19 @@
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
-        <v>301</v>
+        <v>521</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>278</v>
+        <v>499</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>302</v>
+        <v>522</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
@@ -4243,19 +7072,19 @@
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9"/>
       <c r="B34" s="9" t="s">
-        <v>303</v>
+        <v>523</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>304</v>
+        <v>524</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
@@ -4263,19 +7092,19 @@
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9"/>
       <c r="B35" s="9" t="s">
-        <v>273</v>
+        <v>494</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>305</v>
+        <v>525</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
@@ -4283,19 +7112,19 @@
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9"/>
       <c r="B36" s="9" t="s">
-        <v>306</v>
+        <v>526</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>278</v>
+        <v>499</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>307</v>
+        <v>527</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
@@ -4303,19 +7132,19 @@
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9"/>
       <c r="B37" s="9" t="s">
-        <v>224</v>
+        <v>445</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>278</v>
+        <v>499</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>308</v>
+        <v>528</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -4323,19 +7152,19 @@
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9"/>
       <c r="B38" s="9" t="s">
-        <v>234</v>
+        <v>455</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>309</v>
+        <v>529</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>310</v>
+        <v>530</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
@@ -4343,19 +7172,19 @@
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9"/>
       <c r="B39" s="9" t="s">
-        <v>311</v>
+        <v>531</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>288</v>
+        <v>509</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>312</v>
+        <v>532</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="10"/>
@@ -4363,19 +7192,19 @@
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9"/>
       <c r="B40" s="9" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>278</v>
+        <v>499</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>282</v>
+        <v>503</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>313</v>
+        <v>533</v>
       </c>
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
@@ -4401,244 +7230,213 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>314</v>
+        <v>534</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>315</v>
+        <v>535</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>316</v>
+        <v>536</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>317</v>
+        <v>537</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>318</v>
+        <v>538</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>319</v>
+        <v>539</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>322</v>
+        <v>540</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>323</v>
+        <v>541</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>324</v>
+        <v>542</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>328</v>
+        <v>543</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>329</v>
+        <v>540</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>330</v>
+        <v>544</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>332</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="E4" s="10"/>
       <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>333</v>
+        <v>546</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>334</v>
+        <v>540</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>335</v>
+        <v>547</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>337</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="E5" s="10"/>
       <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>338</v>
+        <v>549</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>339</v>
+        <v>540</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>340</v>
+        <v>550</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>342</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="E6" s="10"/>
       <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>343</v>
+        <v>552</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>344</v>
+        <v>540</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>345</v>
+        <v>553</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>347</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>348</v>
+        <v>555</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>349</v>
+        <v>540</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>350</v>
+        <v>556</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>352</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="E8" s="10"/>
       <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>353</v>
+        <v>558</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>354</v>
+        <v>559</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>355</v>
+        <v>560</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>357</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="E9" s="10"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>358</v>
+        <v>562</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>359</v>
+        <v>563</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>360</v>
+        <v>564</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>362</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="E10" s="10"/>
       <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>363</v>
+        <v>566</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>364</v>
+        <v>567</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>365</v>
+        <v>568</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>362</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E11" s="10"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H11"/>
+  <autoFilter ref="A2:F12"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
